--- a/JsonConverter/ExcelFiles/Room.xlsx
+++ b/JsonConverter/ExcelFiles/Room.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="106">
   <si>
     <t xml:space="preserve">캐릭터 고유 ID</t>
   </si>
@@ -28,6 +28,9 @@
     <t xml:space="preserve">Earth/Sky/Any</t>
   </si>
   <si>
+    <t xml:space="preserve">-999 = 모든 층</t>
+  </si>
+  <si>
     <t xml:space="preserve">(name)</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">RequiredCellType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RequiredFloor </t>
   </si>
   <si>
     <t xml:space="preserve">EffectType</t>
@@ -892,7 +898,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -945,6 +951,13 @@
       <name val="&quot;맑은 고딕&quot;"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1029,7 +1042,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1058,6 +1071,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1066,15 +1083,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1328,7 +1345,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V1000"/>
+  <dimension ref="A1:W1000"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.93"/>
@@ -1338,10 +1355,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="28.05"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="11" style="2" width="10.58"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="23" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="28.05"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="12" style="2" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="24" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1356,94 +1373,103 @@
       <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="3"/>
+      <c r="H1" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>3</v>
+      <c r="K2" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="3" s="7" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" s="8" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="6" t="s">
         <v>12</v>
       </c>
+      <c r="H3" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="I3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="2"/>
+      <c r="J3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>2</v>
@@ -1455,27 +1481,30 @@
         <v>150</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="H4" s="3" t="n">
+        <v>-999</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>20</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>2</v>
@@ -1487,27 +1516,30 @@
         <v>150</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="10" t="s">
         <v>26</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>2</v>
@@ -1519,27 +1551,30 @@
         <v>150</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-999</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>31</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2</v>
@@ -1551,27 +1586,30 @@
         <v>150</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-999</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>36</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>2</v>
@@ -1583,27 +1621,30 @@
         <v>150</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-999</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>41</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>2</v>
@@ -1615,27 +1656,30 @@
         <v>150</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-999</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>46</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>2</v>
@@ -1647,27 +1691,30 @@
         <v>150</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>-999</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>51</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>52</v>
+      <c r="A11" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>2</v>
@@ -1679,27 +1726,30 @@
         <v>150</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>-999</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>56</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>57</v>
+      <c r="A12" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>2</v>
@@ -1711,59 +1761,65 @@
         <v>150</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>-999</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>61</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="8" t="n">
+      <c r="A13" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="E13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="H13" s="3" t="n">
+        <v>-999</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>67</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>2</v>
@@ -1775,27 +1831,30 @@
         <v>100</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>-999</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J14" s="10" t="s">
         <v>73</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2</v>
@@ -1807,27 +1866,30 @@
         <v>100</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-999</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>2</v>
@@ -1839,27 +1901,30 @@
         <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-999</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>83</v>
+        <v>73</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>2</v>
@@ -1871,27 +1936,30 @@
         <v>100</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>-999</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>88</v>
+        <v>73</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>2</v>
@@ -1903,27 +1971,30 @@
         <v>100</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-999</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>93</v>
+        <v>73</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>2</v>
@@ -1935,27 +2006,30 @@
         <v>100</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>-999</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>98</v>
+        <v>73</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>2</v>
@@ -1967,28 +2041,32 @@
         <v>100</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-999</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>103</v>
+        <v>73</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/JsonConverter/ExcelFiles/Room.xlsx
+++ b/JsonConverter/ExcelFiles/Room.xlsx
@@ -19,75 +19,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="106">
-  <x:si>
-    <x:t>Room_CounselingRoom</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Using</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>CounselingRoom</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>EffectDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredCellType</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Using</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>DiningRoom</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Using</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>Kitchen</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>Room_Gymnasium</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingGymnasium</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingRestroom</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RequiredFloor </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_DiningRoom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earth/Sky/Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Kitchen</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="105">
+  <x:si>
+    <x:t>Prefabs/Room/Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계단</x:t>
   </x:si>
   <x:si>
     <x:t>Sky</x:t>
@@ -96,28 +39,49 @@
     <x:t>int</x:t>
   </x:si>
   <x:si>
+    <x:t>화장실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상담실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진료실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실3</x:t>
+  </x:si>
+  <x:si>
     <x:t>정원</x:t>
   </x:si>
   <x:si>
+    <x:t>휴게실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식당</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
     <x:t>침실4</x:t>
   </x:si>
   <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실6</x:t>
+  </x:si>
+  <x:si>
     <x:t>사무실</x:t>
   </x:si>
   <x:si>
-    <x:t>침실6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화장실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식당</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실3</x:t>
+    <x:t>침실7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육관</x:t>
   </x:si>
   <x:si>
     <x:t>침실2</x:t>
@@ -126,55 +90,49 @@
     <x:t>침실5</x:t>
   </x:si>
   <x:si>
-    <x:t>상담실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴게실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진료실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주방</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_ConsultationRoom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0006</x:t>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠자는 방6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠자는 방1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠자는 방5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SizeH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠자는 방3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠자는 방4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠자는 방2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지상 정원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠자는 방7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SizeW</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -187,162 +145,6 @@
         <x:color rgb="ff000000"/>
       </x:rPr>
       <x:t>ConsultationRoom</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Garden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Prefabs/Room/Room_</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>DiningRoom</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-999 = 모든 층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sunlight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴게실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사무실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정원 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Lounge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진료실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화장실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EffectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주방 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Garden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상담실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingLounge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식당 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육관 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Stairs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실4 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실1 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실2 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실6 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실5 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingStairs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실3 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실7 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>계단</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t xml:space="preserve"> 효과 설명문</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Prefabs/Room/Room_</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>Kitchen</x:t>
     </x:r>
   </x:si>
   <x:si>
@@ -370,7 +172,106 @@
           </x:rPr>
         </mc:Fallback>
       </mc:AlternateContent>
-      <x:t>Gymnasium</x:t>
+      <x:t>Gym</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_0001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_0002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Meal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_0006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Cure</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_0005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_0004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_0003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_0007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredCellType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EffectDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Using</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>CounselingRoom</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>Earth/Sky/Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RequiredFloor </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Counsel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingGymnasium</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingRestroom</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Using</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>DiningRoom</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>VR룸</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Garden</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Prefabs/Room/</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>Room_Office</x:t>
     </x:r>
   </x:si>
   <x:si>
@@ -378,27 +279,12 @@
       <x:t>Prefabs/Room/Room_</x:t>
     </x:r>
     <x:r>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-          <x:rPr hs:extension="1">
-            <x:rFont val="나눔고딕;맑은 고딕;Noto Sans KR;돋움;돋움체"/>
-            <x:sz val="10"/>
-            <x:color rgb="ff000000"/>
-            <hs:size val="100"/>
-            <hs:ratio val="100"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:rPr>
-        </mc:Choice>
-        <mc:Fallback>
-          <x:rPr>
-            <x:rFont val="나눔고딕;맑은 고딕;Noto Sans KR;돋움;돋움체"/>
-            <x:sz val="10"/>
-            <x:color rgb="ff000000"/>
-          </x:rPr>
-        </mc:Fallback>
-      </mc:AlternateContent>
-      <x:t>Lounge</x:t>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>Counsel</x:t>
     </x:r>
   </x:si>
   <x:si>
@@ -430,8 +316,125 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>Room_Gym</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴게실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Meal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사무실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_0001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화장실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정원 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sunlight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진료실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-999 = 모든 층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상담실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실2 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육관 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingLounge</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EffectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_0007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_0006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실6 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_0005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실4 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_0004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실5 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식당 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실1 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Garden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Stairs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Cure</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_0002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실7 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실3 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingStairs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_0003</x:t>
+  </x:si>
+  <x:si>
     <x:r>
-      <x:t>Prefabs/Room/</x:t>
+      <x:t>계단</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -439,78 +442,7 @@
         <x:sz val="10"/>
         <x:color rgb="ff000000"/>
       </x:rPr>
-      <x:t>Room_Office</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>SizeW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SizeH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지상 정원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방6</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Prefabs/Room/Room_</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>ConsultationRoom</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Prefabs/Room/Room_</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>CounselingRoom</x:t>
+      <x:t xml:space="preserve"> 효과 설명문</x:t>
     </x:r>
   </x:si>
 </x:sst>
@@ -688,7 +620,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -727,6 +659,15 @@
     </x:xf>
     <x:xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1328,7 +1269,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1336,82 +1277,82 @@
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H1" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="I1" s="3"/>
       <x:c r="J1" s="3"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="3" t="s">
-        <x:v>97</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>99</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>99</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G2" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J2" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>99</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:23" s="8" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D3" s="6" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
+      <x:c r="H3" s="7" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G3" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I3" s="6" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J3" s="6" t="s">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="K3" s="8" t="s">
-        <x:v>59</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="L3" s="2"/>
       <x:c r="M3" s="2"/>
@@ -1428,13 +1369,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="3">
         <x:v>2</x:v>
@@ -1446,30 +1387,28 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H4" s="3">
         <x:v>-999</x:v>
       </x:c>
-      <x:c r="I4" s="10" t="s">
-        <x:v>53</x:v>
-      </x:c>
+      <x:c r="I4" s="10"/>
       <x:c r="J4" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K4" s="11" t="s">
-        <x:v>88</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>96</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D5" s="3">
         <x:v>2</x:v>
@@ -1481,30 +1420,30 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H5" s="3">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="10" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K5" s="11" t="s">
-        <x:v>43</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D6" s="3">
         <x:v>2</x:v>
@@ -1516,30 +1455,30 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H6" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K6" s="11" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="K6" s="11" t="s">
-        <x:v>44</x:v>
-      </x:c>
     </x:row>
-    <x:row r="7" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="3">
         <x:v>2</x:v>
@@ -1551,30 +1490,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H7" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K7" s="11" t="s">
-        <x:v>105</x:v>
-      </x:c>
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="L7" s="14"/>
     </x:row>
-    <x:row r="8" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="3">
         <x:v>2</x:v>
@@ -1586,30 +1526,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H8" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K8" s="11" t="s">
-        <x:v>104</x:v>
-      </x:c>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L8" s="14"/>
     </x:row>
-    <x:row r="9" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="9" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="3">
         <x:v>2</x:v>
@@ -1621,30 +1562,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H9" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K9" s="11" t="s">
-        <x:v>84</x:v>
-      </x:c>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L9" s="14"/>
     </x:row>
-    <x:row r="10" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A10" s="3" t="s">
-        <x:v>10</x:v>
+    <x:row r="10" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A10" s="12" t="s">
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D10" s="3">
         <x:v>2</x:v>
@@ -1656,30 +1598,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H10" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>4</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K10" s="11" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L10" s="14"/>
+    </x:row>
+    <x:row r="11" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A11" s="12" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="K10" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A11" s="12" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D11" s="3">
         <x:v>2</x:v>
@@ -1691,33 +1634,34 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H11" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="K11" s="11" t="s">
-        <x:v>85</x:v>
-      </x:c>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L11" s="14"/>
     </x:row>
-    <x:row r="12" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="12" spans="1:23" s="1" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D12" s="3">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E12" s="3">
         <x:v>1</x:v>
@@ -1726,65 +1670,78 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H12" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K12" s="11" t="s">
-        <x:v>86</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="14"/>
+      <x:c r="M12" s="2"/>
+      <x:c r="N12" s="2"/>
+      <x:c r="O12" s="2"/>
+      <x:c r="P12" s="2"/>
+      <x:c r="Q12" s="2"/>
+      <x:c r="R12" s="2"/>
+      <x:c r="S12" s="13"/>
+      <x:c r="T12" s="13"/>
+      <x:c r="U12" s="13"/>
+      <x:c r="V12" s="13"/>
+      <x:c r="W12" s="13"/>
     </x:row>
-    <x:row r="13" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="13" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D13" s="9">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B13" s="15" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D13" s="15">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E13" s="9">
+      <x:c r="E13" s="15">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F13" s="9">
+      <x:c r="F13" s="15">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H13" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I13" s="12" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="J13" s="9" t="s">
-        <x:v>83</x:v>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K13" s="11" t="s">
-        <x:v>87</x:v>
-      </x:c>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L13" s="14"/>
     </x:row>
-    <x:row r="14" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="14" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>100</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D14" s="3">
         <x:v>2</x:v>
@@ -1796,30 +1753,31 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H14" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K14" s="11" t="s">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="L14" s="14"/>
     </x:row>
-    <x:row r="15" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="15" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A15" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D15" s="3">
         <x:v>2</x:v>
@@ -1831,30 +1789,31 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G15" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H15" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I15" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J15" s="3" t="s">
-        <x:v>71</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K15" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L15" s="14"/>
     </x:row>
-    <x:row r="16" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="16" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A16" s="3" t="s">
-        <x:v>79</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>98</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D16" s="3">
         <x:v>2</x:v>
@@ -1866,30 +1825,31 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G16" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H16" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I16" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="K16" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L16" s="14"/>
+    </x:row>
+    <x:row r="17" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A17" s="3" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="J16" s="3" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K16" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A17" s="3" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>95</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D17" s="3">
         <x:v>2</x:v>
@@ -1901,30 +1861,31 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G17" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H17" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I17" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K17" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L17" s="14"/>
     </x:row>
-    <x:row r="18" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="18" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A18" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>102</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D18" s="3">
         <x:v>2</x:v>
@@ -1936,30 +1897,31 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G18" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H18" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I18" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J18" s="3" t="s">
-        <x:v>77</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K18" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L18" s="14"/>
     </x:row>
     <x:row r="19" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A19" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>103</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D19" s="3">
         <x:v>2</x:v>
@@ -1971,30 +1933,30 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G19" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H19" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I19" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J19" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K19" s="11" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A20" s="3" t="s">
-        <x:v>75</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B20" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="3" t="s">
-        <x:v>101</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D20" s="3">
         <x:v>2</x:v>
@@ -2006,19 +1968,19 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G20" s="3" t="s">
-        <x:v>91</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H20" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I20" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J20" s="3" t="s">
-        <x:v>82</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K20" s="11" t="s">
-        <x:v>35</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
@@ -3013,7 +2975,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.51166665554046631" footer="0.51166665554046631"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.51138889789581299" footer="0.51138889789581299"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Room.xlsx
+++ b/JsonConverter/ExcelFiles/Room.xlsx
@@ -19,120 +19,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="105">
-  <x:si>
-    <x:t>Prefabs/Room/Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Battle</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="75">
+  <x:si>
+    <x:t>Sky</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상담실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식당</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴게실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화장실</x:t>
   </x:si>
   <x:si>
     <x:t>계단</x:t>
   </x:si>
   <x:si>
-    <x:t>Sky</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화장실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상담실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실1</x:t>
+    <x:t>VR룸</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육관</x:t>
   </x:si>
   <x:si>
     <x:t>진료실</x:t>
   </x:si>
   <x:si>
-    <x:t>침실3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴게실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식당</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실6</x:t>
-  </x:si>
-  <x:si>
     <x:t>사무실</x:t>
   </x:si>
   <x:si>
-    <x:t>침실7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SizeH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지상 정원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SizeW</x:t>
+    <x:t>Room_Counsel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingGymnasium</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RequiredFloor </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earth/Sky/Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingRestroom</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -144,8 +90,29 @@
         <x:sz val="10"/>
         <x:color rgb="ff000000"/>
       </x:rPr>
-      <x:t>ConsultationRoom</x:t>
+      <x:t>DiningRoom</x:t>
     </x:r>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Garden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Meal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Cure</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -176,42 +143,6 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>Prefabs/Room/Room_0001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Meal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Cure</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Rest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_0007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredCellType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EffectDescription</x:t>
-  </x:si>
-  <x:si>
     <x:r>
       <x:t>Using</x:t>
     </x:r>
@@ -221,27 +152,12 @@
         <x:sz val="10"/>
         <x:color rgb="ff000000"/>
       </x:rPr>
-      <x:t>CounselingRoom</x:t>
+      <x:t>ConsultationRoom</x:t>
     </x:r>
   </x:si>
   <x:si>
-    <x:t>Earth/Sky/Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RequiredFloor </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Counsel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingGymnasium</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingRestroom</x:t>
-  </x:si>
-  <x:si>
     <x:r>
-      <x:t>Using</x:t>
+      <x:t>계단</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -249,43 +165,122 @@
         <x:sz val="10"/>
         <x:color rgb="ff000000"/>
       </x:rPr>
-      <x:t>DiningRoom</x:t>
+      <x:t xml:space="preserve"> 효과 설명문</x:t>
     </x:r>
   </x:si>
   <x:si>
-    <x:t>VR룸</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Garden</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Prefabs/Room/</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>Room_Office</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Prefabs/Room/Room_</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>Counsel</x:t>
-    </x:r>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Meal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Gym</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육관 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화장실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사무실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingLounge</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상담실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-999 = 모든 층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정원 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴게실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sunlight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진료실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EffectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식당 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Stairs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Cure</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingStairs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Garden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실1 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SizeW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SizeH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠자는 방1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지상 정원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -316,125 +311,8 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>Room_Gym</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Rest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴게실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Meal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사무실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화장실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정원 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sunlight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진료실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-999 = 모든 층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상담실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실2 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육관 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingLounge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EffectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실6 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실4 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실5 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식당 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실1 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Garden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Stairs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Cure</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실7 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실3 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingStairs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_0003</x:t>
-  </x:si>
-  <x:si>
     <x:r>
-      <x:t>계단</x:t>
+      <x:t>Prefabs/Room/Room_</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -442,8 +320,40 @@
         <x:sz val="10"/>
         <x:color rgb="ff000000"/>
       </x:rPr>
-      <x:t xml:space="preserve"> 효과 설명문</x:t>
+      <x:t>Counsel</x:t>
     </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Prefabs/Room/</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>Room_Office</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>EffectDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Using</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>CounselingRoom</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>RequiredCellType</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1269,7 +1179,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>78</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1277,82 +1187,82 @@
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H1" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I1" s="3"/>
       <x:c r="J1" s="3"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:23" s="8" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="I3" s="6" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="J3" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K3" s="8" t="s">
-        <x:v>71</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L3" s="2"/>
       <x:c r="M3" s="2"/>
@@ -1369,13 +1279,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D4" s="3">
         <x:v>2</x:v>
@@ -1387,28 +1297,28 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H4" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I4" s="10"/>
       <x:c r="J4" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K4" s="11" t="s">
-        <x:v>62</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>96</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D5" s="3">
         <x:v>2</x:v>
@@ -1420,30 +1330,30 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="3">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="10" t="s">
-        <x:v>77</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K5" s="11" t="s">
-        <x:v>61</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>79</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="3">
         <x:v>2</x:v>
@@ -1455,30 +1365,30 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H6" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
-        <x:v>75</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="K6" s="11" t="s">
-        <x:v>60</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D7" s="3">
         <x:v>2</x:v>
@@ -1490,31 +1400,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
-        <x:v>82</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K7" s="11" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L7" s="14"/>
     </x:row>
     <x:row r="8" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>98</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="3">
         <x:v>2</x:v>
@@ -1526,31 +1436,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H8" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K8" s="11" t="s">
-        <x:v>44</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L8" s="14"/>
     </x:row>
     <x:row r="9" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D9" s="3">
         <x:v>2</x:v>
@@ -1562,31 +1472,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H9" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
-        <x:v>94</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K9" s="11" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L9" s="14"/>
     </x:row>
     <x:row r="10" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A10" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D10" s="3">
         <x:v>2</x:v>
@@ -1598,31 +1508,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H10" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
-        <x:v>84</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K10" s="11" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L10" s="14"/>
     </x:row>
     <x:row r="11" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="3">
         <x:v>2</x:v>
@@ -1634,31 +1544,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H11" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L11" s="14"/>
     </x:row>
     <x:row r="12" spans="1:23" s="1" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>2</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D12" s="3">
         <x:v>4</x:v>
@@ -1670,19 +1580,19 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H12" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K12" s="11" t="s">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L12" s="14"/>
       <x:c r="M12" s="2"/>
@@ -1699,13 +1609,13 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B13" s="15" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D13" s="15">
         <x:v>1</x:v>
@@ -1717,31 +1627,31 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H13" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I13" s="12" t="s">
-        <x:v>102</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>104</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K13" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L13" s="14"/>
     </x:row>
     <x:row r="14" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D14" s="3">
         <x:v>2</x:v>
@@ -1753,235 +1663,103 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H14" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
-        <x:v>95</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K14" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="L14" s="14"/>
     </x:row>
     <x:row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A15" s="3" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B15" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="3" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D15" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E15" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F15" s="3">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G15" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H15" s="3">
-        <x:v>-999</x:v>
-      </x:c>
-      <x:c r="I15" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J15" s="3" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="K15" s="11" t="s">
-        <x:v>41</x:v>
-      </x:c>
+      <x:c r="A15" s="3"/>
+      <x:c r="B15" s="3"/>
+      <x:c r="C15" s="3"/>
+      <x:c r="D15" s="3"/>
+      <x:c r="E15" s="3"/>
+      <x:c r="F15" s="3"/>
+      <x:c r="G15" s="3"/>
+      <x:c r="H15" s="3"/>
+      <x:c r="I15" s="3"/>
+      <x:c r="J15" s="3"/>
+      <x:c r="K15" s="11"/>
       <x:c r="L15" s="14"/>
     </x:row>
     <x:row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A16" s="3" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B16" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C16" s="3" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D16" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E16" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F16" s="3">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G16" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H16" s="3">
-        <x:v>-999</x:v>
-      </x:c>
-      <x:c r="I16" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J16" s="3" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="K16" s="11" t="s">
-        <x:v>48</x:v>
-      </x:c>
+      <x:c r="A16" s="3"/>
+      <x:c r="B16" s="3"/>
+      <x:c r="C16" s="3"/>
+      <x:c r="D16" s="3"/>
+      <x:c r="E16" s="3"/>
+      <x:c r="F16" s="3"/>
+      <x:c r="G16" s="3"/>
+      <x:c r="H16" s="3"/>
+      <x:c r="I16" s="3"/>
+      <x:c r="J16" s="3"/>
+      <x:c r="K16" s="11"/>
       <x:c r="L16" s="14"/>
     </x:row>
     <x:row r="17" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A17" s="3" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B17" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C17" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D17" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E17" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F17" s="3">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G17" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H17" s="3">
-        <x:v>-999</x:v>
-      </x:c>
-      <x:c r="I17" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J17" s="3" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="K17" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
+      <x:c r="A17" s="3"/>
+      <x:c r="B17" s="3"/>
+      <x:c r="C17" s="3"/>
+      <x:c r="D17" s="3"/>
+      <x:c r="E17" s="3"/>
+      <x:c r="F17" s="3"/>
+      <x:c r="G17" s="3"/>
+      <x:c r="H17" s="3"/>
+      <x:c r="I17" s="3"/>
+      <x:c r="J17" s="3"/>
+      <x:c r="K17" s="11"/>
       <x:c r="L17" s="14"/>
     </x:row>
     <x:row r="18" spans="1:12" ht="15.75" customHeight="1">
-      <x:c r="A18" s="3" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B18" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C18" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D18" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E18" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F18" s="3">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G18" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H18" s="3">
-        <x:v>-999</x:v>
-      </x:c>
-      <x:c r="I18" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J18" s="3" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="K18" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
+      <x:c r="A18" s="3"/>
+      <x:c r="B18" s="3"/>
+      <x:c r="C18" s="3"/>
+      <x:c r="D18" s="3"/>
+      <x:c r="E18" s="3"/>
+      <x:c r="F18" s="3"/>
+      <x:c r="G18" s="3"/>
+      <x:c r="H18" s="3"/>
+      <x:c r="I18" s="3"/>
+      <x:c r="J18" s="3"/>
+      <x:c r="K18" s="11"/>
       <x:c r="L18" s="14"/>
     </x:row>
     <x:row r="19" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A19" s="3" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B19" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C19" s="3" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D19" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E19" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F19" s="3">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G19" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H19" s="3">
-        <x:v>-999</x:v>
-      </x:c>
-      <x:c r="I19" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J19" s="3" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="K19" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
+      <x:c r="A19" s="3"/>
+      <x:c r="B19" s="3"/>
+      <x:c r="C19" s="3"/>
+      <x:c r="D19" s="3"/>
+      <x:c r="E19" s="3"/>
+      <x:c r="F19" s="3"/>
+      <x:c r="G19" s="3"/>
+      <x:c r="H19" s="3"/>
+      <x:c r="I19" s="3"/>
+      <x:c r="J19" s="3"/>
+      <x:c r="K19" s="11"/>
     </x:row>
     <x:row r="20" spans="1:11" ht="15.75" customHeight="1">
-      <x:c r="A20" s="3" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B20" s="3" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C20" s="3" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D20" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E20" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F20" s="3">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G20" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H20" s="3">
-        <x:v>-999</x:v>
-      </x:c>
-      <x:c r="I20" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J20" s="3" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="K20" s="11" t="s">
-        <x:v>49</x:v>
-      </x:c>
+      <x:c r="A20" s="3"/>
+      <x:c r="B20" s="3"/>
+      <x:c r="C20" s="3"/>
+      <x:c r="D20" s="3"/>
+      <x:c r="E20" s="3"/>
+      <x:c r="F20" s="3"/>
+      <x:c r="G20" s="3"/>
+      <x:c r="H20" s="3"/>
+      <x:c r="I20" s="3"/>
+      <x:c r="J20" s="3"/>
+      <x:c r="K20" s="11"/>
     </x:row>
     <x:row r="21" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A21" s="3"/>

--- a/JsonConverter/ExcelFiles/Room.xlsx
+++ b/JsonConverter/ExcelFiles/Room.xlsx
@@ -21,98 +21,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="75">
   <x:si>
-    <x:t>Sky</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상담실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식당</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴게실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화장실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VR룸</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진료실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사무실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Counsel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingGymnasium</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RequiredFloor </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earth/Sky/Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingRestroom</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Using</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>DiningRoom</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Garden</x:t>
+    <x:t>Prefabs/Room/Room_Cure</x:t>
   </x:si>
   <x:si>
     <x:t>Prefabs/Room/Room_Rest</x:t>
   </x:si>
   <x:si>
+    <x:t>Prefabs/Room/Room_Sleep</x:t>
+  </x:si>
+  <x:si>
     <x:t>Prefabs/Room/Room_Meal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Cure</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -156,8 +74,53 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>Earth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SizeW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SizeH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지상 정원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠자는 방1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingRestroom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingGymnasium</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RequiredFloor </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earth/Sky/Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Counsel</x:t>
+  </x:si>
+  <x:si>
     <x:r>
-      <x:t>계단</x:t>
+      <x:t>Using</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -165,122 +128,107 @@
         <x:sz val="10"/>
         <x:color rgb="ff000000"/>
       </x:rPr>
-      <x:t xml:space="preserve"> 효과 설명문</x:t>
+      <x:t>DiningRoom</x:t>
     </x:r>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Rest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Meal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Gym</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육관 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화장실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사무실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingLounge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상담실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-999 = 모든 층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정원 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴게실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sunlight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진료실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EffectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식당 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Stairs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Cure</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingStairs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Garden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실1 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SizeW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SizeH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지상 정원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:r>
+      <x:t>Prefabs/Room/Room_</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>Counsel</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Garden</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Prefabs/Room/</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>Room_Office</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴게실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VR룸</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화장실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식당</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계단</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상담실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진료실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sky</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사무실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredCellType</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Using</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>CounselingRoom</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>EffectDescription</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -311,8 +259,89 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>Room_Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정원 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상담실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Meal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사무실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-999 = 모든 층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육관 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴게실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingLounge</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진료실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화장실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sunlight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EffectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Gym</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식당 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingStairs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실1 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Stairs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Cure</x:t>
+  </x:si>
+  <x:si>
     <x:r>
-      <x:t>Prefabs/Room/Room_</x:t>
+      <x:t>계단</x:t>
     </x:r>
     <x:r>
       <x:rPr>
@@ -320,40 +349,11 @@
         <x:sz val="10"/>
         <x:color rgb="ff000000"/>
       </x:rPr>
-      <x:t>Counsel</x:t>
+      <x:t xml:space="preserve"> 효과 설명문</x:t>
     </x:r>
   </x:si>
   <x:si>
-    <x:r>
-      <x:t>Prefabs/Room/</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>Room_Office</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>EffectDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Using</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>CounselingRoom</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>RequiredCellType</x:t>
+    <x:t>Room_Sun</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1179,7 +1179,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1187,82 +1187,82 @@
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H1" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I1" s="3"/>
       <x:c r="J1" s="3"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G2" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J2" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:23" s="8" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
-        <x:v>74</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I3" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J3" s="6" t="s">
-        <x:v>72</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="L3" s="2"/>
       <x:c r="M3" s="2"/>
@@ -1279,13 +1279,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="3">
         <x:v>2</x:v>
@@ -1297,28 +1297,28 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H4" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I4" s="10"/>
       <x:c r="J4" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K4" s="11" t="s">
-        <x:v>71</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="3">
         <x:v>2</x:v>
@@ -1330,30 +1330,30 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H5" s="3">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="10" t="s">
-        <x:v>47</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K5" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="3">
         <x:v>2</x:v>
@@ -1365,30 +1365,30 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K6" s="11" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D7" s="3">
         <x:v>2</x:v>
@@ -1400,31 +1400,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H7" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K7" s="11" t="s">
-        <x:v>70</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L7" s="14"/>
     </x:row>
     <x:row r="8" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D8" s="3">
         <x:v>2</x:v>
@@ -1436,31 +1436,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H8" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>29</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K8" s="11" t="s">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L8" s="14"/>
     </x:row>
     <x:row r="9" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D9" s="3">
         <x:v>2</x:v>
@@ -1472,31 +1472,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H9" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K9" s="11" t="s">
-        <x:v>26</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L9" s="14"/>
     </x:row>
     <x:row r="10" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A10" s="12" t="s">
-        <x:v>36</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D10" s="3">
         <x:v>2</x:v>
@@ -1508,31 +1508,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H10" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K10" s="11" t="s">
-        <x:v>28</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L10" s="14"/>
     </x:row>
     <x:row r="11" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D11" s="3">
         <x:v>2</x:v>
@@ -1544,31 +1544,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H11" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K11" s="11" t="s">
-        <x:v>25</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L11" s="14"/>
     </x:row>
     <x:row r="12" spans="1:23" s="1" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D12" s="3">
         <x:v>4</x:v>
@@ -1580,19 +1580,19 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H12" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K12" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L12" s="14"/>
       <x:c r="M12" s="2"/>
@@ -1609,13 +1609,13 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B13" s="15" t="s">
-        <x:v>9</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>9</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D13" s="15">
         <x:v>1</x:v>
@@ -1627,31 +1627,31 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H13" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I13" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K13" s="11" t="s">
-        <x:v>69</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L13" s="14"/>
     </x:row>
     <x:row r="14" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D14" s="3">
         <x:v>2</x:v>
@@ -1663,19 +1663,19 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H14" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="K14" s="11" t="s">
-        <x:v>58</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L14" s="14"/>
     </x:row>

--- a/JsonConverter/ExcelFiles/Room.xlsx
+++ b/JsonConverter/ExcelFiles/Room.xlsx
@@ -19,18 +19,49 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="75">
-  <x:si>
-    <x:t>Prefabs/Room/Room_Cure</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Rest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Meal</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="83">
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SizeW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SizeH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredCellType</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Using</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>CounselingRoom</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>EffectDescription</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -74,49 +105,85 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>Earth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SizeW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SizeH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지상 정원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠자는 방1</x:t>
+    <x:t>Prefabs/Room/Room_Cure</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Meal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화장실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상담실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계단</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식당</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sky</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VR룸</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정원</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사무실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴게실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>치료실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무리 은퇴했더라도 건강을 위해 가벼운 운동은 해야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지하 건물이기에 하루에 한 번 영웅들에게 햇빛을 쬐어주는 일을 빼먹어서는 안됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오로지 영웅들만을 위한 H.B 프로젝트가 진행되는 공간입니다! 자주 들러주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earth/Sky/Any</x:t>
   </x:si>
   <x:si>
     <x:t>UsingRestroom</x:t>
   </x:si>
   <x:si>
+    <x:t>Room_Counsel</x:t>
+  </x:si>
+  <x:si>
     <x:t>UsingGymnasium</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">RequiredFloor </x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earth/Sky/Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Counsel</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -132,6 +199,28 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>Prefabs/Room/Room_Garden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Prefabs/Room/</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>Room_Office</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
     <x:r>
       <x:t>Prefabs/Room/Room_</x:t>
     </x:r>
@@ -143,92 +232,6 @@
       </x:rPr>
       <x:t>Counsel</x:t>
     </x:r>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Garden</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Prefabs/Room/</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>Room_Office</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴게실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VR룸</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화장실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식당</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상담실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정원</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진료실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sky</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사무실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredCellType</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Using</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>CounselingRoom</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>EffectDescription</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -259,82 +262,85 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>정원 효과 설명문</x:t>
+  </x:si>
+  <x:si>
     <x:t>Room_Rest</x:t>
   </x:si>
   <x:si>
+    <x:t>Room_Shower</x:t>
+  </x:si>
+  <x:si>
     <x:t>Room_Battle</x:t>
   </x:si>
   <x:si>
     <x:t>Room_Sleep</x:t>
   </x:si>
   <x:si>
+    <x:t>BuildCost</x:t>
+  </x:si>
+  <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>BuildCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정원 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Shower</x:t>
-  </x:si>
-  <x:si>
     <x:t>상담실 효과 설명문</x:t>
   </x:si>
   <x:si>
+    <x:t>침실1 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사무실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-999 = 모든 층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육관 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingLounge</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화장실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진료실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴게실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EffectType</x:t>
+  </x:si>
+  <x:si>
     <x:t>Room_Meal</x:t>
   </x:si>
   <x:si>
-    <x:t>사무실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-999 = 모든 층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육관 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴게실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingLounge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진료실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화장실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
     <x:t>Sunlight</x:t>
   </x:si>
   <x:si>
-    <x:t>EffectType</x:t>
-  </x:si>
-  <x:si>
     <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
     <x:t>Room_Gym</x:t>
   </x:si>
   <x:si>
+    <x:t>UsingStairs</x:t>
+  </x:si>
+  <x:si>
     <x:t>식당 효과 설명문</x:t>
   </x:si>
   <x:si>
-    <x:t>UsingStairs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실1 효과 설명문</x:t>
+    <x:t>Room_Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Stairs</x:t>
   </x:si>
   <x:si>
     <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Stairs</x:t>
   </x:si>
   <x:si>
     <x:t>Room_Cure</x:t>
@@ -353,7 +359,25 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>Room_Sun</x:t>
+    <x:t>전성기를 점차 잊어가며 트라우마를 겪고 있는 요양원의 영웅들에게 상담 시간은 매우 중요합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임, 책 등 영웅들이 취미를 즐길 수 있도록 준비해두었습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전한 H.B 프로젝트이지만 아주 가끔 다치는 경우가 있을 수도 있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신이 일하는 곳입니다. 상점 이용, 마감 등 많은 일을 할 수 있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앞으로 입소한 영웅들이 지내게 될 방입니다. 좋지는 않지만 나쁘지도 않죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들의 건강을 위한 건강식이 준비되어 있습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화장실의 중요성은 이미 잘 알고 계시겠죠?</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1166,7 +1190,7 @@
   <x:cols>
     <x:col min="1" max="1" width="22.9296875" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="18.25" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="23.109375" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="83.28515625" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="6.25" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="5.87890625" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="8.91796875" style="1" customWidth="1"/>
@@ -1179,7 +1203,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1187,82 +1211,82 @@
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H1" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I1" s="3"/>
       <x:c r="J1" s="3"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="11.949999999999999">
       <x:c r="A2" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G2" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J2" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:23" s="8" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E3" s="6" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I3" s="6" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="J3" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K3" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L3" s="2"/>
       <x:c r="M3" s="2"/>
@@ -1279,13 +1303,13 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D4" s="3">
         <x:v>2</x:v>
@@ -1297,28 +1321,28 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H4" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I4" s="10"/>
       <x:c r="J4" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K4" s="11" t="s">
-        <x:v>26</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D5" s="3">
         <x:v>2</x:v>
@@ -1330,30 +1354,30 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H5" s="3">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="10" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K5" s="11" t="s">
-        <x:v>25</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D6" s="3">
         <x:v>2</x:v>
@@ -1365,30 +1389,30 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H6" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K6" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D7" s="3">
         <x:v>2</x:v>
@@ -1400,31 +1424,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H7" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>43</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K7" s="11" t="s">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L7" s="14"/>
     </x:row>
     <x:row r="8" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D8" s="3">
         <x:v>2</x:v>
@@ -1436,31 +1460,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H8" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K8" s="11" t="s">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L8" s="14"/>
     </x:row>
     <x:row r="9" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D9" s="3">
         <x:v>2</x:v>
@@ -1472,31 +1496,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H9" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K9" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L9" s="14"/>
     </x:row>
     <x:row r="10" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A10" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="3">
         <x:v>2</x:v>
@@ -1508,31 +1532,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H10" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="K10" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L10" s="14"/>
     </x:row>
     <x:row r="11" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D11" s="3">
         <x:v>2</x:v>
@@ -1544,31 +1568,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H11" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K11" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L11" s="14"/>
     </x:row>
     <x:row r="12" spans="1:23" s="1" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D12" s="3">
         <x:v>4</x:v>
@@ -1580,19 +1604,19 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H12" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K12" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L12" s="14"/>
       <x:c r="M12" s="2"/>
@@ -1609,13 +1633,13 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B13" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D13" s="15">
         <x:v>1</x:v>
@@ -1627,31 +1651,31 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H13" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I13" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K13" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L13" s="14"/>
     </x:row>
     <x:row r="14" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D14" s="3">
         <x:v>2</x:v>
@@ -1663,19 +1687,19 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H14" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K14" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L14" s="14"/>
     </x:row>

--- a/JsonConverter/ExcelFiles/Room.xlsx
+++ b/JsonConverter/ExcelFiles/Room.xlsx
@@ -19,33 +19,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="83">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SizeW</x:t>
+  </x:si>
+  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
+    <x:t>SizeH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earth</x:t>
+  </x:si>
+  <x:si>
     <x:t>Battle</x:t>
   </x:si>
   <x:si>
-    <x:t>Earth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SizeW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SizeH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredCellType</x:t>
+    <x:t>Room_Counsel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingGymnasium</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingRestroom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Earth/Sky/Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RequiredFloor </x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -57,11 +69,33 @@
         <x:sz val="10"/>
         <x:color rgb="ff000000"/>
       </x:rPr>
-      <x:t>CounselingRoom</x:t>
+      <x:t>DiningRoom</x:t>
     </x:r>
   </x:si>
   <x:si>
-    <x:t>EffectDescription</x:t>
+    <x:t>Prefabs/Room/Room_Meal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Cure</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Using</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>ConsultationRoom</x:t>
+    </x:r>
   </x:si>
   <x:si>
     <x:r>
@@ -92,133 +126,61 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:r>
-      <x:t>Using</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>ConsultationRoom</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Cure</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Meal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Rest</x:t>
+    <x:t>화장실의 중요성은 이미 잘 알고 계시겠죠?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴게실</x:t>
   </x:si>
   <x:si>
     <x:t>화장실</x:t>
   </x:si>
   <x:si>
+    <x:t>식당</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육관</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
     <x:t>상담실</x:t>
   </x:si>
   <x:si>
+    <x:t>사무실</x:t>
+  </x:si>
+  <x:si>
     <x:t>계단</x:t>
   </x:si>
   <x:si>
+    <x:t>Any</x:t>
+  </x:si>
+  <x:si>
+    <x:t>치료실</x:t>
+  </x:si>
+  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>식당</x:t>
-  </x:si>
-  <x:si>
     <x:t>Sky</x:t>
   </x:si>
   <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
     <x:t>VR룸</x:t>
   </x:si>
   <x:si>
-    <x:t>Any</x:t>
-  </x:si>
-  <x:si>
     <x:t>정원</x:t>
   </x:si>
   <x:si>
-    <x:t>체육관</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사무실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴게실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>치료실</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무리 은퇴했더라도 건강을 위해 가벼운 운동은 해야합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지하 건물이기에 하루에 한 번 영웅들에게 햇빛을 쬐어주는 일을 빼먹어서는 안됩니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오로지 영웅들만을 위한 H.B 프로젝트가 진행되는 공간입니다! 자주 들러주세요!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Earth/Sky/Any</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingRestroom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Counsel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingGymnasium</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RequiredFloor </x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Using</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>DiningRoom</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Garden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prefabs/Room/Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>Prefabs/Room/</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="&quot;맑은 고딕&quot;"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>Room_Office</x:t>
-    </x:r>
+    <x:t>MaxCapacity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전한 H.B 프로젝트이지만 아주 가끔 다치는 경우가 있을 수도 있습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당신이 일하는 곳입니다. 상점 이용, 마감 등 많은 일을 할 수 있습니다.</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -262,88 +224,66 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>정원 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Rest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BuildCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상담실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>침실1 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사무실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-999 = 모든 층</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체육관 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingLounge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화장실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진료실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴게실 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EffectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Meal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sunlight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Gym</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UsingStairs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식당 효과 설명문</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Sun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Stairs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Office</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Room_Cure</x:t>
+    <x:t>오로지 영웅들만을 위한 H.B 프로젝트가 진행되는 공간입니다! 자주 들러주세요!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지하 건물이기에 하루에 한 번 영웅들에게 햇빛을 쬐어주는 일을 빼먹어서는 안됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전성기를 점차 잊어가며 트라우마를 겪고 있는 요양원의 영웅들에게 상담 시간은 매우 중요합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Prefabs/Room/</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>Room_Office</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prefabs/Room/Room_Garden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅들의 건강을 위한 건강식이 준비되어 있습니다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>앞으로 입소한 영웅들이 지내게 될 방입니다. 좋지는 않지만 나쁘지도 않죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>Using</x:t>
+    </x:r>
+    <x:r>
+      <x:rPr>
+        <x:rFont val="&quot;맑은 고딕&quot;"/>
+        <x:sz val="10"/>
+        <x:color rgb="ff000000"/>
+      </x:rPr>
+      <x:t>CounselingRoom</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:t>RequiredCellType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EffectDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무리 은퇴했더라도 건강을 위해 가벼운 운동은 해야합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>게임, 책 등 영웅들이 취미를 즐길 수 있도록 준비해두었습니다.</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -359,25 +299,91 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t>전성기를 점차 잊어가며 트라우마를 겪고 있는 요양원의 영웅들에게 상담 시간은 매우 중요합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>게임, 책 등 영웅들이 취미를 즐길 수 있도록 준비해두었습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전한 H.B 프로젝트이지만 아주 가끔 다치는 경우가 있을 수도 있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당신이 일하는 곳입니다. 상점 이용, 마감 등 많은 일을 할 수 있습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앞으로 입소한 영웅들이 지내게 될 방입니다. 좋지는 않지만 나쁘지도 않죠.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅들의 건강을 위한 건강식이 준비되어 있습니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화장실의 중요성은 이미 잘 알고 계시겠죠?</x:t>
+    <x:t>Room_Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>침실1 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체육관 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingLounge</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상담실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화장실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BuildCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-999 = 모든 층</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사무실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정원 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진료실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Office</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sunlight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UsingStairs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Gym</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴게실 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식당 효과 설명문</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Meal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Stairs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EffectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Room_Cure</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수용 인원</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1197,13 +1203,14 @@
     <x:col min="7" max="7" width="22.34765625" style="1" customWidth="1"/>
     <x:col min="8" max="9" width="16.84765625" style="1" customWidth="1"/>
     <x:col min="10" max="11" width="28.046875" style="1" customWidth="1"/>
-    <x:col min="12" max="18" width="10.578125" style="2"/>
+    <x:col min="12" max="12" width="10.578125" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="18" width="10.578125" style="2"/>
     <x:col min="24" max="16384" width="10.578125" style="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>61</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1211,17 +1218,20 @@
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H1" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I1" s="3"/>
       <x:c r="J1" s="3"/>
+      <x:c r="L1" s="2" t="s">
+        <x:v>84</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" spans="1:11" ht="11.949999999999999">
+    <x:row r="2" spans="1:12" ht="11.949999999999999">
       <x:c r="A2" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
         <x:v>0</x:v>
@@ -1230,19 +1240,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G2" s="4" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
         <x:v>0</x:v>
@@ -1252,43 +1262,48 @@
       </x:c>
       <x:c r="K2" s="3" t="s">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="L2" s="2" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:23" s="8" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G3" s="6" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I3" s="6" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J3" s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="K3" s="8" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="L3" s="2"/>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L3" s="2" t="s">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="M3" s="2"/>
       <x:c r="N3" s="2"/>
       <x:c r="O3" s="2"/>
@@ -1301,15 +1316,15 @@
       <x:c r="V3" s="9"/>
       <x:c r="W3" s="9"/>
     </x:row>
-    <x:row r="4" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="4" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>79</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D4" s="3">
         <x:v>2</x:v>
@@ -1321,28 +1336,31 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H4" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I4" s="10"/>
       <x:c r="J4" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K4" s="11" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="L4" s="2">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
-    <x:row r="5" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="5" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C5" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D5" s="3">
         <x:v>2</x:v>
@@ -1354,30 +1372,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H5" s="3">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="10" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J5" s="3" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="K5" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="K5" s="11" t="s">
-        <x:v>41</x:v>
+      <x:c r="L5" s="2">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:11" ht="15.75" customHeight="1">
+    <x:row r="6" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>82</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D6" s="3">
         <x:v>2</x:v>
@@ -1389,30 +1410,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I6" s="12" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J6" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K6" s="11" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L6" s="2">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D7" s="3">
         <x:v>2</x:v>
@@ -1424,31 +1448,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G7" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H7" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I7" s="12" t="s">
-        <x:v>9</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K7" s="11" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L7" s="14"/>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L7" s="14">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>78</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D8" s="3">
         <x:v>2</x:v>
@@ -1460,31 +1486,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G8" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H8" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I8" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J8" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K8" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="L8" s="14"/>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L8" s="14">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>81</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="3">
         <x:v>2</x:v>
@@ -1496,31 +1524,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G9" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H9" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I9" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K9" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L9" s="14"/>
+      <x:c r="L9" s="14">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A10" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D10" s="3">
         <x:v>2</x:v>
@@ -1532,31 +1562,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G10" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H10" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I10" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="K10" s="11" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="L10" s="14"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L10" s="14">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>77</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D11" s="3">
         <x:v>2</x:v>
@@ -1568,31 +1600,33 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G11" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H11" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I11" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J11" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K11" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="L11" s="14"/>
+      <x:c r="L11" s="14">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" spans="1:23" s="1" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D12" s="3">
         <x:v>4</x:v>
@@ -1604,21 +1638,23 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G12" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H12" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I12" s="12" t="s">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J12" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K12" s="11" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="L12" s="14"/>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="L12" s="14">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="M12" s="2"/>
       <x:c r="N12" s="2"/>
       <x:c r="O12" s="2"/>
@@ -1633,13 +1669,13 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B13" s="15" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D13" s="15">
         <x:v>1</x:v>
@@ -1651,31 +1687,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G13" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H13" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I13" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>75</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K13" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L13" s="14"/>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L13" s="14">
+        <x:v>100</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D14" s="3">
         <x:v>2</x:v>
@@ -1687,21 +1725,23 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G14" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H14" s="3">
         <x:v>-999</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K14" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L14" s="14"/>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="L14" s="14">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A15" s="3"/>
